--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MS_Scores_ZScore" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MS_Assignments_All" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation_vs_Melanie" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended_Method_Comparison" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best_MS_Assignments" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4123,6 +4125,2723 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>warm_n</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>green_n</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unpl_n</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>other_n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MS Z-Score</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ensemble orig+Z</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MS original</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warm rescale</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warm + Z-Score</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TF-IDF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TF-IDF + warm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>68</v>
+      </c>
+      <c r="F8" t="n">
+        <v>36</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Top-5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>91</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Top-5 + warm</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="n">
+        <v>66</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ensemble warm+Z</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MS Rohstoffe</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Squared Z-Score</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warm + Sq.Z-Score</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="n">
+        <v>37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cosine</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="n">
+        <v>54</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cosine + warm</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rez.-Nr.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MS_cluster</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>panel_cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>185.028</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>185.043P</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>185.046</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>185.086</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>185.090P</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>185.091</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>185.133</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>185.178HP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>185.237H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>185.239</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>185.267</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>185.291</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>185.294</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>185.309P</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>185.314</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>185.321</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>185.339P</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>185.382P</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>185.471</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>185.507P</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>185.513P</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>185.514</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>185.578P</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>185.615</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>185.621P</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>185.644P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>185.664</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>185.675P</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>185.727P</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>185.741P</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>185.748P</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>185.796P</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>185.902P</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>185.922P</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>185.984P</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>186.179P</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>186.190P</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>186.192</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>186.277P</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>186.293P</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>186.395P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>186.396P</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>186.490P</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>186.569P</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>186.821</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>186.950P</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>186.981P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>186.985P</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>187.004P</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>187.015P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>187.061P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>187.064P</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>187.119P</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>187.167P</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>187.246P</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>187.365</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>187.414P</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>187.482P</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>187.483P</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>187.507P</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>187.519P</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>187.521P</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>187.522P</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>187.567P</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>187.571P</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>187.608P</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>187.657P</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>187.662P</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>187.694P</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>187.695P</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>187.746P</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>187.752P</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>187.753P</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>187.772</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>187.773P</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>187.776</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>187.783P</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>187.786P</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>187.787P</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>187.791P</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>187.799P</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>187.800P</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>187.826P</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>187.829P</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>187.834P</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>187.843P</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>187.870P</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>187.871P</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>187.885P</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>187.886P</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>187.892P</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>187.893P</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>187.894P</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>187.895P</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>187.896P</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>187.897P</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>187.907</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>187.914P</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>187.916P</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>187.920P</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>187.921P</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>187.923P</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>188.118P</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>188.375P</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>188.402P</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>188.412P</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>188.462KHP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>188.481KHP</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>188.491P</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>188.560P</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>188.628P</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>188.639P</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>188.656P</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>188.668P</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>188.740P</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>188.819</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>188.820</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>188.822</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>188.866</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>188.894</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>188.977</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>188.992</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>189.012</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>189.051</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>189.068</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>189.075</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -23415,7 +23415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23426,82 +23426,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_pred</t>
+          <t>Melanie_label</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Our_pred</t>
+          <t>MS original</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_Unpleasant</t>
+          <t>MS Z-Score</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_warm</t>
+          <t>MS Warm rescale</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_green</t>
+          <t>MS Warm+Z-Score</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_floral</t>
+          <t>MS TF-IDF</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_citrus</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Melanie_exotic</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Melanie_Outlayer</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_Unpleasant</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_warm</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_green</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_floral</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_citrus</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_exotic</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Ours_Outlayer</t>
+          <t>MS Rohstoffe</t>
         </is>
       </c>
     </row>
@@ -23518,50 +23473,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>26.513</v>
-      </c>
-      <c r="E2" t="n">
-        <v>69.877</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12.788</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.324</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.994</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8.487</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.058</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.2564</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.6261</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.8045</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.1349</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.3794</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.4469</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.0057</v>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>unpleasant ✗</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>unpleasant ✗</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>unpleasant ✗</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>warm ✓</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -23577,50 +23515,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>75.684</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.019</v>
-      </c>
-      <c r="F3" t="n">
-        <v>38.284</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.276</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8.273</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8.285</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8622</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.3231</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3919</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0567</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.2056</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.2057</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>unpleasant ✓</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -23636,50 +23557,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>21.943</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35.943</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12.246</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.907</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.6563</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.2895</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.8703</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.6257</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -23695,50 +23599,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.901</v>
-      </c>
-      <c r="E5" t="n">
-        <v>22.836</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.055</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.055</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.494</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7286</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.1302</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.7055</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.2767</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.3038</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.3038</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unpleasant ✗</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -23754,50 +23641,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4.896</v>
-      </c>
-      <c r="E6" t="n">
-        <v>56.176</v>
-      </c>
-      <c r="F6" t="n">
-        <v>16.324</v>
-      </c>
-      <c r="G6" t="n">
-        <v>75.005</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.878</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.878</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.3098</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3.4712</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.0123</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.5231</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.3097</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.3097</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>floral ✓</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>floral ✓</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>warm ✗</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>green ✗</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -4192,13 +4192,13 @@
         <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
         <v>15</v>
@@ -4500,13 +4500,13 @@
         <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
         <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
         <v>19</v>
@@ -4528,13 +4528,13 @@
         <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
         <v>23</v>
@@ -4652,12 +4652,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -6726,12 +6726,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -14913,7 +14913,7 @@
         <v>73.59229999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>11.552</v>
+        <v>21.5054</v>
       </c>
       <c r="D2" t="n">
         <v>43.503</v>
@@ -14941,7 +14941,7 @@
         <v>4.9448</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4145</v>
+        <v>5.9856</v>
       </c>
       <c r="D3" t="n">
         <v>3.6596</v>
@@ -14969,7 +14969,7 @@
         <v>4.9433</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6397</v>
+        <v>6.2099</v>
       </c>
       <c r="D4" t="n">
         <v>3.6585</v>
@@ -15389,7 +15389,7 @@
         <v>0.7672</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4726</v>
+        <v>2.4394</v>
       </c>
       <c r="D19" t="n">
         <v>7.6868</v>
@@ -15865,7 +15865,7 @@
         <v>97.0471</v>
       </c>
       <c r="C36" t="n">
-        <v>13.4533</v>
+        <v>16.6769</v>
       </c>
       <c r="D36" t="n">
         <v>14.568</v>
@@ -16285,7 +16285,7 @@
         <v>18.6571</v>
       </c>
       <c r="C51" t="n">
-        <v>45.626</v>
+        <v>49.3111</v>
       </c>
       <c r="D51" t="n">
         <v>28.7457</v>
@@ -18189,7 +18189,7 @@
         <v>4.9433</v>
       </c>
       <c r="C119" t="n">
-        <v>3.6397</v>
+        <v>6.2099</v>
       </c>
       <c r="D119" t="n">
         <v>3.6585</v>
@@ -18357,7 +18357,7 @@
         <v>36.8084</v>
       </c>
       <c r="C125" t="n">
-        <v>28.9088</v>
+        <v>69.87690000000001</v>
       </c>
       <c r="D125" t="n">
         <v>12.7875</v>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>unpleasant</t>
+          <t>warm</t>
         </is>
       </c>
     </row>
@@ -23415,7 +23415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23426,37 +23426,82 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Melanie_label</t>
+          <t>Melanie_pred</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MS original</t>
+          <t>Our_pred</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MS Z-Score</t>
+          <t>Melanie_Unpleasant</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>MS Warm rescale</t>
+          <t>Melanie_warm</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>MS Warm+Z-Score</t>
+          <t>Melanie_green</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>MS TF-IDF</t>
+          <t>Melanie_floral</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MS Rohstoffe</t>
+          <t>Melanie_citrus</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Melanie_exotic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Melanie_Outlayer</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_Unpleasant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_warm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_green</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_floral</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_citrus</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_exotic</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ours_Outlayer</t>
         </is>
       </c>
     </row>
@@ -23473,33 +23518,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>warm ✓</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>unpleasant ✗</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>unpleasant ✗</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>unpleasant ✗</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>warm ✓</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>26.513</v>
+      </c>
+      <c r="E2" t="n">
+        <v>69.877</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.324</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.994</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.487</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.058</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.2564</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.6261</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.8045</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0057</v>
       </c>
     </row>
     <row r="3">
@@ -23515,33 +23577,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unpleasant ✓</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>75.684</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16.019</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38.284</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.276</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.273</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.285</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -23557,33 +23636,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>21.943</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.943</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.246</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.907</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.6563</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.2895</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.8703</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9219000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -23599,33 +23695,50 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>unpleasant ✗</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.901</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22.836</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7286</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.1302</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -23641,33 +23754,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>floral ✓</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>floral ✓</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>warm ✗</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>green ✗</t>
-        </is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56.176</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.324</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.878</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.878</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.4712</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.0123</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5231</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -5607,11 +5607,7 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -5896,11 +5892,7 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -8376,11 +8368,6 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
       <c r="D59" t="n">
         <v>0.4559</v>
       </c>
@@ -8816,11 +8803,6 @@
       <c r="B76" t="inlineStr">
         <is>
           <t>exotic</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>dairy</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -20724,19 +20706,9 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>dairy</t>
         </is>
       </c>
     </row>
@@ -21353,19 +21325,9 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>warm</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>dairy</t>
         </is>
       </c>
     </row>

--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -18,6 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation_vs_Melanie" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended_Method_Comparison" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best_MS_Assignments" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZScore_All_Predictions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZScore_Predictions_Slim" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5607,7 +5609,6 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -5892,7 +5893,6 @@
           <t>exotic</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -6827,6 +6827,8027 @@
         <is>
           <t>warm</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rez.-Nr.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ZScore_cluster</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ZScore_panel_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Score_Unpleasant</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Score_warm</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Score_green</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Score_floral</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Score_citrus</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Score_exotic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Score_Outlayer</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>in_verkostung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>185.028</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>73.59229999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.5054</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.503</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18.2518</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.2482</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15.3365</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.635999999999999</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>187.657P</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>50.9853</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.0634</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32.1672</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.9441</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.9342</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1557</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>187.892P</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>33.325</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29.0626</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.0459</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.1441</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.4897</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.056100000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>187.246P</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>47.6751</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.1643</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.1819</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.9132</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.3445</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>187.167P</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>28.5995</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.0838</v>
+      </c>
+      <c r="F6" t="n">
+        <v>20.0992</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.2617</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.9175</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>187.119P</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.7073</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.1156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5716</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.7163</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>186.985P</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.2582</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.7766</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.1779</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>186.950P</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>124.3375</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60.5653</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.5491</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.0266</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.648</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9071</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>187.829P</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>22.1632</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.9908</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.2563</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>185.984P</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>54.5153</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.9498</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.4564</v>
+      </c>
+      <c r="G11" t="n">
+        <v>32.0314</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.4586</v>
+      </c>
+      <c r="I11" t="n">
+        <v>29.1756</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>185.922P</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>97.0471</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.6769</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.568</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43.6884</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.4197</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23.4452</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>185.748P</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>39.565</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27.4517</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34.0317</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.1994</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.6629</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.0053</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>188.560P</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40.0755</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.3287</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.0634</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.9688</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.9025</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>185.471</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>29.129</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.2773</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20.2006</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.7124</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2604</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.9064</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>187.921P</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>187.826P</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>185.090P</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.8828</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.4173</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.6589</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>185.267</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20.8734</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.8947</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.6979</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.7511</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.5316</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>187.772</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68.0699</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>130.3337</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>187.414P</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>8.2859</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.1035</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.8224</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.1597</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.4986</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.4162</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>187.786P</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.0382</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.5227</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12.8657</v>
+      </c>
+      <c r="G22" t="n">
+        <v>28.7335</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>187.776</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.0703</v>
+      </c>
+      <c r="E23" t="n">
+        <v>35.225</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.2361</v>
+      </c>
+      <c r="G23" t="n">
+        <v>47.0323</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.0587</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.0587</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>187.834P</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.2183</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.462</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.995</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26.7392</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.799</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.8939</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>189.068</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8968</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.8928</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.5748</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26.1533</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8968</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8968</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>187.894P</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20.4776</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43.085</v>
+      </c>
+      <c r="F26" t="n">
+        <v>39.3677</v>
+      </c>
+      <c r="G26" t="n">
+        <v>199.5967</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.2894</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5771</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>186.981P</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.3624</v>
+      </c>
+      <c r="E27" t="n">
+        <v>13.2784</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20.8513</v>
+      </c>
+      <c r="G27" t="n">
+        <v>35.894</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.0628</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.2459</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>187.923P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>27.2367</v>
+      </c>
+      <c r="E28" t="n">
+        <v>14.2279</v>
+      </c>
+      <c r="F28" t="n">
+        <v>19.8907</v>
+      </c>
+      <c r="G28" t="n">
+        <v>68.6022</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.5196</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.189</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>188.375P</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.7617</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.8701</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.9451</v>
+      </c>
+      <c r="G29" t="n">
+        <v>35.1323</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6508</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9474</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>185.902P</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>97.40989999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>18.5085</v>
+      </c>
+      <c r="F30" t="n">
+        <v>26.9347</v>
+      </c>
+      <c r="G30" t="n">
+        <v>182.2039</v>
+      </c>
+      <c r="H30" t="n">
+        <v>36.1403</v>
+      </c>
+      <c r="I30" t="n">
+        <v>34.0737</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>185.796P</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.7079</v>
+      </c>
+      <c r="E31" t="n">
+        <v>52.1087</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12.2525</v>
+      </c>
+      <c r="G31" t="n">
+        <v>122.0993</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.0475</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.0503</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>187.004P</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18.6571</v>
+      </c>
+      <c r="E32" t="n">
+        <v>49.3111</v>
+      </c>
+      <c r="F32" t="n">
+        <v>28.7457</v>
+      </c>
+      <c r="G32" t="n">
+        <v>57.1338</v>
+      </c>
+      <c r="H32" t="n">
+        <v>38.3993</v>
+      </c>
+      <c r="I32" t="n">
+        <v>18.5357</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>185.514</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2.4614</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.8176</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.4313</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.5994</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2141</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>185.615</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>36.6255</v>
+      </c>
+      <c r="E34" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11.6595</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.3986</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.4218</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.4218</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.9554</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>185.291</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.6341</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.4855</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.4191</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.7747000000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.0911</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.0911</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>187.519P</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>19.7366</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30.9309</v>
+      </c>
+      <c r="F36" t="n">
+        <v>55.1285</v>
+      </c>
+      <c r="G36" t="n">
+        <v>22.4225</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.5135</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.5135</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>187.483P</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.0063</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11.3758</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36.9645</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.9091</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8.1511</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11.1786</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>187.482P</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.3079</v>
+      </c>
+      <c r="E38" t="n">
+        <v>67.5926</v>
+      </c>
+      <c r="F38" t="n">
+        <v>153.2567</v>
+      </c>
+      <c r="G38" t="n">
+        <v>94.7042</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.6935</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.345</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>188.462KHP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20.2907</v>
+      </c>
+      <c r="E39" t="n">
+        <v>57.6758</v>
+      </c>
+      <c r="F39" t="n">
+        <v>58.6627</v>
+      </c>
+      <c r="G39" t="n">
+        <v>37.3183</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.6828</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>187.843P</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>9.426</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.9944</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14.1919</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.1787</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.9522</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>187.907</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.1784</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>187.015P</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7.2039</v>
+      </c>
+      <c r="E42" t="n">
+        <v>26.9466</v>
+      </c>
+      <c r="F42" t="n">
+        <v>68.22620000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>21.1567</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.9924</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.5153</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>185.382P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.3079</v>
+      </c>
+      <c r="E43" t="n">
+        <v>67.5926</v>
+      </c>
+      <c r="F43" t="n">
+        <v>153.2567</v>
+      </c>
+      <c r="G43" t="n">
+        <v>94.7042</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.6935</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.345</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>26.3363</v>
+      </c>
+      <c r="E44" t="n">
+        <v>20.1163</v>
+      </c>
+      <c r="F44" t="n">
+        <v>30.0456</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9.585100000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.153</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.8859</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>185.513P</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16.4448</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.3446</v>
+      </c>
+      <c r="F45" t="n">
+        <v>55.0906</v>
+      </c>
+      <c r="G45" t="n">
+        <v>37.9835</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5.4633</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.4633</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>185.133</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.9613</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.8702</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.1341</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>187.773P</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4216</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.8226</v>
+      </c>
+      <c r="F47" t="n">
+        <v>23.384</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.4435</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.391</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>186.569P</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8875</v>
+      </c>
+      <c r="E48" t="n">
+        <v>17.4349</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33.6703</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6.3775</v>
+      </c>
+      <c r="H48" t="n">
+        <v>9.557499999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>13.8415</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>185.339P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.4394</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.6868</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.9617</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5.701</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>187.783P</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.8016</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.2105</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.2902</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.6202</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>188.639P</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>17.009</v>
+      </c>
+      <c r="E51" t="n">
+        <v>38.7968</v>
+      </c>
+      <c r="F51" t="n">
+        <v>68.9995</v>
+      </c>
+      <c r="G51" t="n">
+        <v>8.9901</v>
+      </c>
+      <c r="H51" t="n">
+        <v>14.4736</v>
+      </c>
+      <c r="I51" t="n">
+        <v>14.5683</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.7302</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>187.791P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.9909</v>
+      </c>
+      <c r="E52" t="n">
+        <v>11.8326</v>
+      </c>
+      <c r="F52" t="n">
+        <v>20.4015</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.1993</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.8975</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.8975</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>188.118P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14.1296</v>
+      </c>
+      <c r="E53" t="n">
+        <v>22.0431</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22.293</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.1809</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.7448</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.0364</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>187.787P</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4213</v>
+      </c>
+      <c r="E54" t="n">
+        <v>11.7059</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18.3657</v>
+      </c>
+      <c r="G54" t="n">
+        <v>12.5076</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.8854</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.8854</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>186.821</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2.9613</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.2991</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.1341</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>188.894</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15.2281</v>
+      </c>
+      <c r="E56" t="n">
+        <v>34.0578</v>
+      </c>
+      <c r="F56" t="n">
+        <v>48.5461</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10.6438</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6.888</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.888</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>188.402P</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>188.412P</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>32.9695</v>
+      </c>
+      <c r="E58" t="n">
+        <v>15.0083</v>
+      </c>
+      <c r="F58" t="n">
+        <v>49.3189</v>
+      </c>
+      <c r="G58" t="n">
+        <v>17.8986</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10.8249</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.8249</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>189.051</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4.3315</v>
+      </c>
+      <c r="E59" t="n">
+        <v>51.4631</v>
+      </c>
+      <c r="F59" t="n">
+        <v>30.2171</v>
+      </c>
+      <c r="G59" t="n">
+        <v>11.5253</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.5753</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.5753</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>187.886P</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>4.1871</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.3733</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.1459</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6.3784</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.1324</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>187.871P</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5.9006</v>
+      </c>
+      <c r="E61" t="n">
+        <v>86.84910000000001</v>
+      </c>
+      <c r="F61" t="n">
+        <v>50.4419</v>
+      </c>
+      <c r="G61" t="n">
+        <v>53.4246</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.0952</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>187.870P</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>4.8144</v>
+      </c>
+      <c r="E62" t="n">
+        <v>20.1231</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.7529</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.6818</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.6258</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3.2604</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>188.822</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>9.3728</v>
+      </c>
+      <c r="E63" t="n">
+        <v>99.11620000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.9564</v>
+      </c>
+      <c r="G63" t="n">
+        <v>16.7749</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.7931</v>
+      </c>
+      <c r="I63" t="n">
+        <v>6.2904</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>188.740P</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>98.8934</v>
+      </c>
+      <c r="F64" t="n">
+        <v>55.2079</v>
+      </c>
+      <c r="G64" t="n">
+        <v>16.0803</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>20</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>187.885P</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>9.9613</v>
+      </c>
+      <c r="E65" t="n">
+        <v>39.7309</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.3162</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5.3161</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.1558</v>
+      </c>
+      <c r="J65" t="n">
+        <v>8.934200000000001</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>8.3918</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10.5711</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5.9321</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.3176</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.2595</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.1073</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>188.481KHP</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6.7242</v>
+      </c>
+      <c r="E67" t="n">
+        <v>211.4448</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15.7199</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5.7349</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9598</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>188.668P</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7.5885</v>
+      </c>
+      <c r="E68" t="n">
+        <v>53.3219</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8.622999999999999</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.9104</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>188.491P</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>6.0453</v>
+      </c>
+      <c r="E69" t="n">
+        <v>99.1185</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12.0981</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20.7729</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.0916</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2.0916</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>188.866</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6.2804</v>
+      </c>
+      <c r="E70" t="n">
+        <v>9.002700000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.5551</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4.1447</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>188.628P</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>32.3769</v>
+      </c>
+      <c r="E71" t="n">
+        <v>128.4911</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.1004</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24.8679</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4.0856</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5.0599</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>25.0815</v>
+      </c>
+      <c r="E72" t="n">
+        <v>41.3184</v>
+      </c>
+      <c r="F72" t="n">
+        <v>29.6061</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6.8168</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.3704</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4.3704</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>187.920P</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>20.6153</v>
+      </c>
+      <c r="E73" t="n">
+        <v>34.2575</v>
+      </c>
+      <c r="F73" t="n">
+        <v>23.7341</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6.2196</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7.1452</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>187.916P</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="E74" t="n">
+        <v>20.9977</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>188.977</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>36.8084</v>
+      </c>
+      <c r="E75" t="n">
+        <v>69.87690000000001</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.7875</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4.3238</v>
+      </c>
+      <c r="H75" t="n">
+        <v>5.9938</v>
+      </c>
+      <c r="I75" t="n">
+        <v>8.486800000000001</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3.0582</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>188.820</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>32.4523</v>
+      </c>
+      <c r="E76" t="n">
+        <v>38.8635</v>
+      </c>
+      <c r="F76" t="n">
+        <v>35.9429</v>
+      </c>
+      <c r="G76" t="n">
+        <v>12.2457</v>
+      </c>
+      <c r="H76" t="n">
+        <v>6.4196</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7.9066</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>187.914P</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>18.5782</v>
+      </c>
+      <c r="E77" t="n">
+        <v>48.9334</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4.7244</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.0108</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.0979</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3.1567</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>188.656P</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3.5802</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7.2591</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.0415</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.3252</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.5551</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2.5633</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>188.992</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>21.912</v>
+      </c>
+      <c r="E79" t="n">
+        <v>64.51130000000001</v>
+      </c>
+      <c r="F79" t="n">
+        <v>28.3571</v>
+      </c>
+      <c r="G79" t="n">
+        <v>23.1084</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4.3174</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5.9492</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>189.012</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>22.5458</v>
+      </c>
+      <c r="E80" t="n">
+        <v>94.0384</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13.3249</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20.1008</v>
+      </c>
+      <c r="H80" t="n">
+        <v>12.1124</v>
+      </c>
+      <c r="I80" t="n">
+        <v>18.8313</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>187.897P</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4.5913</v>
+      </c>
+      <c r="E81" t="n">
+        <v>42.5168</v>
+      </c>
+      <c r="F81" t="n">
+        <v>24.5477</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5.9766</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="I81" t="n">
+        <v>7.4006</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>187.896P</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3.6127</v>
+      </c>
+      <c r="E82" t="n">
+        <v>22.164</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.2033</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>187.895P</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3.3134</v>
+      </c>
+      <c r="E83" t="n">
+        <v>59.901</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8.0435</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7854</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.2217</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>187.893P</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4511</v>
+      </c>
+      <c r="E84" t="n">
+        <v>86.9131</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.474600000000001</v>
+      </c>
+      <c r="G84" t="n">
+        <v>29.9633</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.4217</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.5362</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>188.819</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4.9433</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6.2099</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3.6585</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.7626</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.7013</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.0862</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.3498</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>187.567P</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>18.6145</v>
+      </c>
+      <c r="E86" t="n">
+        <v>75.6401</v>
+      </c>
+      <c r="F86" t="n">
+        <v>34.8771</v>
+      </c>
+      <c r="G86" t="n">
+        <v>25.094</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.6744</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4.732</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>187.799P</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>22.5244</v>
+      </c>
+      <c r="E87" t="n">
+        <v>88.6009</v>
+      </c>
+      <c r="F87" t="n">
+        <v>26.8843</v>
+      </c>
+      <c r="G87" t="n">
+        <v>26.788</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.189</v>
+      </c>
+      <c r="I87" t="n">
+        <v>4.2393</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>185.727P</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>67.8526</v>
+      </c>
+      <c r="F88" t="n">
+        <v>19.1377</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>9</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>185.675P</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2.5878</v>
+      </c>
+      <c r="E89" t="n">
+        <v>38.0355</v>
+      </c>
+      <c r="F89" t="n">
+        <v>23.575</v>
+      </c>
+      <c r="G89" t="n">
+        <v>15.2307</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.0604</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.0604</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>185.664</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6.7701</v>
+      </c>
+      <c r="E90" t="n">
+        <v>130.9903</v>
+      </c>
+      <c r="F90" t="n">
+        <v>29.3487</v>
+      </c>
+      <c r="G90" t="n">
+        <v>23.6799</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3.5099</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4.2296</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>185.644P</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>23.376</v>
+      </c>
+      <c r="E91" t="n">
+        <v>36.6295</v>
+      </c>
+      <c r="F91" t="n">
+        <v>18.3665</v>
+      </c>
+      <c r="G91" t="n">
+        <v>13.7596</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4.2782</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5.5461</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>185.621P</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>14.3102</v>
+      </c>
+      <c r="E92" t="n">
+        <v>36.7015</v>
+      </c>
+      <c r="F92" t="n">
+        <v>19.1214</v>
+      </c>
+      <c r="G92" t="n">
+        <v>10.4261</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4.2762</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5.8125</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>185.578P</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>20.7586</v>
+      </c>
+      <c r="E93" t="n">
+        <v>45.0372</v>
+      </c>
+      <c r="F93" t="n">
+        <v>20.3097</v>
+      </c>
+      <c r="G93" t="n">
+        <v>19.5773</v>
+      </c>
+      <c r="H93" t="n">
+        <v>15.8566</v>
+      </c>
+      <c r="I93" t="n">
+        <v>13.2585</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>185.507P</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4.3736</v>
+      </c>
+      <c r="E94" t="n">
+        <v>93.4085</v>
+      </c>
+      <c r="F94" t="n">
+        <v>21.6316</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4.8774</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3.2127</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3.2174</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>185.321</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.1219</v>
+      </c>
+      <c r="E95" t="n">
+        <v>46.4521</v>
+      </c>
+      <c r="F95" t="n">
+        <v>39.6023</v>
+      </c>
+      <c r="G95" t="n">
+        <v>6.7059</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5.2551</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5.2551</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>185.314</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7.3587</v>
+      </c>
+      <c r="E96" t="n">
+        <v>19.2317</v>
+      </c>
+      <c r="F96" t="n">
+        <v>13.6523</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5.9725</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.4554</v>
+      </c>
+      <c r="I96" t="n">
+        <v>4.4427</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>185.309P</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>13.3931</v>
+      </c>
+      <c r="E97" t="n">
+        <v>69.2282</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12.8181</v>
+      </c>
+      <c r="G97" t="n">
+        <v>65.1437</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5.8855</v>
+      </c>
+      <c r="I97" t="n">
+        <v>9.503500000000001</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>185.294</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>17.7313</v>
+      </c>
+      <c r="E98" t="n">
+        <v>49.1204</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12.8352</v>
+      </c>
+      <c r="G98" t="n">
+        <v>7.5104</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3.7973</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3.7973</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>185.239</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>34.6267</v>
+      </c>
+      <c r="E99" t="n">
+        <v>53.7186</v>
+      </c>
+      <c r="F99" t="n">
+        <v>18.5336</v>
+      </c>
+      <c r="G99" t="n">
+        <v>14.7946</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4.9951</v>
+      </c>
+      <c r="I99" t="n">
+        <v>7.5328</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>185.237H</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>15.4218</v>
+      </c>
+      <c r="E100" t="n">
+        <v>36.9564</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9.936299999999999</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.7105</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.7652</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2.7652</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>185.178HP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>17.4001</v>
+      </c>
+      <c r="E101" t="n">
+        <v>37.7272</v>
+      </c>
+      <c r="F101" t="n">
+        <v>32.0618</v>
+      </c>
+      <c r="G101" t="n">
+        <v>18.7931</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4.9554</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4.9554</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>185.091</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2.3023</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4.9827</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.2409</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.4848</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>185.086</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>4.879</v>
+      </c>
+      <c r="E103" t="n">
+        <v>79.59439999999999</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13.5598</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5.0913</v>
+      </c>
+      <c r="H103" t="n">
+        <v>5.6246</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4.482</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>185.046</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.0677</v>
+      </c>
+      <c r="E104" t="n">
+        <v>43.7524</v>
+      </c>
+      <c r="F104" t="n">
+        <v>20.5615</v>
+      </c>
+      <c r="G104" t="n">
+        <v>24.8279</v>
+      </c>
+      <c r="H104" t="n">
+        <v>10.0677</v>
+      </c>
+      <c r="I104" t="n">
+        <v>10.0677</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>4.9433</v>
+      </c>
+      <c r="E105" t="n">
+        <v>6.2099</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3.6585</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3.7626</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.7013</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.0862</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.3498</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>185.043P</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4.9448</v>
+      </c>
+      <c r="E106" t="n">
+        <v>5.9856</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3.6596</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3.7638</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.7015</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.0865</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.3502</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>185.741P</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="E107" t="n">
+        <v>19.6227</v>
+      </c>
+      <c r="F107" t="n">
+        <v>7.3458</v>
+      </c>
+      <c r="G107" t="n">
+        <v>10.9654</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>187.800P</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="E108" t="n">
+        <v>25.5377</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.2175</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.2592</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>186.179P</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>7.1535</v>
+      </c>
+      <c r="E109" t="n">
+        <v>164.7909</v>
+      </c>
+      <c r="F109" t="n">
+        <v>35.381</v>
+      </c>
+      <c r="G109" t="n">
+        <v>12.008</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5.2547</v>
+      </c>
+      <c r="I109" t="n">
+        <v>5.2624</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>186.192</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>13.0347</v>
+      </c>
+      <c r="E110" t="n">
+        <v>35.0452</v>
+      </c>
+      <c r="F110" t="n">
+        <v>27.8034</v>
+      </c>
+      <c r="G110" t="n">
+        <v>19.732</v>
+      </c>
+      <c r="H110" t="n">
+        <v>8.682399999999999</v>
+      </c>
+      <c r="I110" t="n">
+        <v>8.682399999999999</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>187.753P</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>29.1203</v>
+      </c>
+      <c r="E111" t="n">
+        <v>74.4302</v>
+      </c>
+      <c r="F111" t="n">
+        <v>25.9562</v>
+      </c>
+      <c r="G111" t="n">
+        <v>20.6575</v>
+      </c>
+      <c r="H111" t="n">
+        <v>4.1468</v>
+      </c>
+      <c r="I111" t="n">
+        <v>4.1468</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>187.752P</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>28.8133</v>
+      </c>
+      <c r="E112" t="n">
+        <v>73.64570000000001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>25.6827</v>
+      </c>
+      <c r="G112" t="n">
+        <v>20.4398</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4.1031</v>
+      </c>
+      <c r="I112" t="n">
+        <v>4.1031</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>187.746P</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>19.6205</v>
+      </c>
+      <c r="E113" t="n">
+        <v>152.4628</v>
+      </c>
+      <c r="F113" t="n">
+        <v>39.2266</v>
+      </c>
+      <c r="G113" t="n">
+        <v>14.5945</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5.3128</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.9676</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>187.695P</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7.5431</v>
+      </c>
+      <c r="E114" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="F114" t="n">
+        <v>5.7514</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4.4707</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.1604</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>187.694P</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>38.0133</v>
+      </c>
+      <c r="E115" t="n">
+        <v>63.7212</v>
+      </c>
+      <c r="F115" t="n">
+        <v>27.0994</v>
+      </c>
+      <c r="G115" t="n">
+        <v>20.7913</v>
+      </c>
+      <c r="H115" t="n">
+        <v>5.4262</v>
+      </c>
+      <c r="I115" t="n">
+        <v>7.153</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>187.662P</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="E116" t="n">
+        <v>59.7215</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8.484</v>
+      </c>
+      <c r="G116" t="n">
+        <v>27.7856</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>187.608P</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>23.3158</v>
+      </c>
+      <c r="E117" t="n">
+        <v>64.26090000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>26.5199</v>
+      </c>
+      <c r="G117" t="n">
+        <v>21.9434</v>
+      </c>
+      <c r="H117" t="n">
+        <v>5.5589</v>
+      </c>
+      <c r="I117" t="n">
+        <v>7.5366</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>187.571P</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>12.8246</v>
+      </c>
+      <c r="E118" t="n">
+        <v>72.251</v>
+      </c>
+      <c r="F118" t="n">
+        <v>15.1559</v>
+      </c>
+      <c r="G118" t="n">
+        <v>26.6587</v>
+      </c>
+      <c r="H118" t="n">
+        <v>7.6707</v>
+      </c>
+      <c r="I118" t="n">
+        <v>10.6536</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>187.522P</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>9.6279</v>
+      </c>
+      <c r="E119" t="n">
+        <v>126.8061</v>
+      </c>
+      <c r="F119" t="n">
+        <v>21.6362</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5.2395</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4.7316</v>
+      </c>
+      <c r="I119" t="n">
+        <v>4.9337</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>187.521P</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>59.1299</v>
+      </c>
+      <c r="E120" t="n">
+        <v>87.8788</v>
+      </c>
+      <c r="F120" t="n">
+        <v>5.4447</v>
+      </c>
+      <c r="G120" t="n">
+        <v>66.3896</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2.1492</v>
+      </c>
+      <c r="I120" t="n">
+        <v>50.5332</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>187.507P</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>32.3769</v>
+      </c>
+      <c r="E121" t="n">
+        <v>128.4911</v>
+      </c>
+      <c r="F121" t="n">
+        <v>21.1004</v>
+      </c>
+      <c r="G121" t="n">
+        <v>24.8679</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4.0856</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5.0599</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>187.365</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>23.6995</v>
+      </c>
+      <c r="E122" t="n">
+        <v>115.8424</v>
+      </c>
+      <c r="F122" t="n">
+        <v>22.9386</v>
+      </c>
+      <c r="G122" t="n">
+        <v>12.6309</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4.8059</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6.5627</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>187.064P</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>28.0305</v>
+      </c>
+      <c r="E123" t="n">
+        <v>48.7704</v>
+      </c>
+      <c r="F123" t="n">
+        <v>18.8007</v>
+      </c>
+      <c r="G123" t="n">
+        <v>33.7716</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1.6721</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2.2491</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>187.061P</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3.7489</v>
+      </c>
+      <c r="E124" t="n">
+        <v>108.7111</v>
+      </c>
+      <c r="F124" t="n">
+        <v>20.5561</v>
+      </c>
+      <c r="G124" t="n">
+        <v>34.6089</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.9138</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3.8474</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>186.490P</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>14.4156</v>
+      </c>
+      <c r="E125" t="n">
+        <v>67.73050000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>25.0916</v>
+      </c>
+      <c r="G125" t="n">
+        <v>32.967</v>
+      </c>
+      <c r="H125" t="n">
+        <v>5.8407</v>
+      </c>
+      <c r="I125" t="n">
+        <v>6.2676</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>186.396P</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>32.3786</v>
+      </c>
+      <c r="E126" t="n">
+        <v>128.4946</v>
+      </c>
+      <c r="F126" t="n">
+        <v>21.0989</v>
+      </c>
+      <c r="G126" t="n">
+        <v>24.8699</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4.0868</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5.0602</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>186.395P</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>6.2953</v>
+      </c>
+      <c r="E127" t="n">
+        <v>135.3398</v>
+      </c>
+      <c r="F127" t="n">
+        <v>22.2499</v>
+      </c>
+      <c r="G127" t="n">
+        <v>26.1915</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4.3045</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.3299</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>186.293P</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1.5043</v>
+      </c>
+      <c r="E128" t="n">
+        <v>42.6692</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.1298</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6.1045</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1.6393</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>186.277P</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>42.6599</v>
+      </c>
+      <c r="E129" t="n">
+        <v>102.2117</v>
+      </c>
+      <c r="F129" t="n">
+        <v>27.4868</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7.4964</v>
+      </c>
+      <c r="H129" t="n">
+        <v>7.6503</v>
+      </c>
+      <c r="I129" t="n">
+        <v>7.6503</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.4007</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>186.190P</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>21.6155</v>
+      </c>
+      <c r="E130" t="n">
+        <v>31.5346</v>
+      </c>
+      <c r="F130" t="n">
+        <v>27.2437</v>
+      </c>
+      <c r="G130" t="n">
+        <v>18.3721</v>
+      </c>
+      <c r="H130" t="n">
+        <v>8.880599999999999</v>
+      </c>
+      <c r="I130" t="n">
+        <v>8.880599999999999</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>189.075</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>14.5464</v>
+      </c>
+      <c r="E131" t="n">
+        <v>40.5172</v>
+      </c>
+      <c r="F131" t="n">
+        <v>26.5933</v>
+      </c>
+      <c r="G131" t="n">
+        <v>27.7725</v>
+      </c>
+      <c r="H131" t="n">
+        <v>8.0015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>8.157</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ZScore_cluster</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ZScore_panel_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>in_verkostung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>185.028</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>187.657P</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>187.892P</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>187.246P</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>187.167P</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>187.119P</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>186.985P</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>186.950P</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>187.829P</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>185.984P</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>185.922P</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>185.748P</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>188.560P</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>185.471</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>187.921P</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>187.826P</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>185.090P</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>185.267</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unpleasant</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>187.772</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>187.414P</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>exotic</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>187.786P</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>187.776</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>187.834P</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>189.068</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>187.894P</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>186.981P</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>187.923P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>188.375P</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>185.902P</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>185.796P</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>187.004P</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>185.514</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>185.615</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>185.291</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>187.519P</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>187.483P</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>187.482P</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>188.462KHP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>187.843P</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>187.907</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>187.015P</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>185.382P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>187.796P</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>185.513P</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>185.133</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>187.773P</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>186.569P</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>185.339P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>187.783P</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>188.639P</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>187.791P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>188.118P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>187.787P</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>186.821</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>188.894</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>188.402P</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>188.412P</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>189.051</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>187.886P</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>187.871P</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>187.870P</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>188.822</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>188.740P</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>187.885P</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>189.014</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>188.481KHP</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>188.668P</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>188.491P</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>188.866</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>188.628P</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>188.976</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>187.920P</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>187.916P</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>188.977</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>188.820</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>187.914P</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>188.656P</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>188.992</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>189.012</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>187.897P</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>187.896P</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>187.895P</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>187.893P</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>188.819</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>187.567P</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>187.799P</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>185.727P</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>185.675P</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>185.664</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>185.644P</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>185.621P</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>185.578P</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>185.507P</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>185.321</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>185.314</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>185.309P</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>185.294</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>185.239</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>185.237H</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>185.178HP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>185.091</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>185.086</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>185.046</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>185.044</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>185.043P</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>185.741P</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>187.800P</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>186.179P</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>186.192</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>187.753P</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>187.752P</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>187.746P</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>187.695P</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>187.694P</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>187.662P</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>187.608P</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>187.571P</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>187.522P</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>187.521P</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>187.507P</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>187.365</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>187.064P</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>187.061P</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>186.490P</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>186.396P</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>186.395P</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>186.293P</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>186.277P</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>186.190P</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>189.075</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10256,7 +18277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10277,15 +18298,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>n_yes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
@@ -10307,19 +18333,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>warm ✓</t>
-        </is>
+      <c r="D2" t="n">
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>warm ✓</t>
+          <t>warm ok</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>warm ✓</t>
+          <t>warm ok</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>warm ok</t>
         </is>
       </c>
     </row>
@@ -10339,19 +18368,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>warm ✓</t>
-        </is>
+      <c r="D3" t="n">
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>warm ✓</t>
+          <t>warm ok</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>warm ✓</t>
+          <t>warm ok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>warm ok</t>
         </is>
       </c>
     </row>
@@ -10371,19 +18403,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Walderdbeere ✓</t>
-        </is>
+      <c r="D4" t="n">
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Walderdbeere ✓</t>
+          <t>Walderdbeere ok</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>warm ✗</t>
+          <t>Walderdbeere ok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>warm x</t>
         </is>
       </c>
     </row>
@@ -10403,19 +18438,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>floral ✓</t>
-        </is>
+      <c r="D5" t="n">
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>floral ✓</t>
+          <t>floral ok</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>warm ✗</t>
+          <t>floral ok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>warm x</t>
         </is>
       </c>
     </row>
@@ -10435,19 +18473,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>green ✓</t>
-        </is>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>green ✓</t>
+          <t>green ok</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>green ✓</t>
+          <t>green ok</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>green ok</t>
         </is>
       </c>
     </row>
@@ -10467,19 +18508,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>dairy ✓</t>
-        </is>
+      <c r="D7" t="n">
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dairy ✓</t>
+          <t>dairy ok</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>warm ✗</t>
+          <t>dairy ok</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>warm x</t>
         </is>
       </c>
     </row>
@@ -10499,19 +18543,22 @@
           <t>corrected</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dairy ✗</t>
-        </is>
+      <c r="D8" t="n">
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dairy ✗</t>
+          <t>dairy x</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>green ✗</t>
+          <t>dairy x</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>green x</t>
         </is>
       </c>
     </row>
@@ -10531,19 +18578,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
+      <c r="D9" t="n">
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>unpleasant ✓</t>
+          <t>unpleasant ok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>unpleasant ✓</t>
+          <t>unpleasant ok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>unpleasant ok</t>
         </is>
       </c>
     </row>
@@ -10563,19 +18613,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>unpleasant ✓</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>unpleasant ✓</t>
+          <t>unpleasant ok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>unpleasant ✓</t>
+          <t>unpleasant ok</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>unpleasant ok</t>
         </is>
       </c>
     </row>
@@ -10595,19 +18648,22 @@
           <t>endorsed</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>fruity ✓</t>
-        </is>
+      <c r="D11" t="n">
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>fruity ✓</t>
+          <t>fruity ok</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unpleasant ✗</t>
+          <t>fruity ok</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>unpleasant x</t>
         </is>
       </c>
     </row>

--- a/outputs/scoring_ms_assessment.xlsx
+++ b/outputs/scoring_ms_assessment.xlsx
@@ -6840,7 +6840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6899,6 +6899,11 @@
           <t>in_verkostung</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GT_panel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -6940,6 +6945,11 @@
       <c r="K2" t="b">
         <v>1</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -6981,6 +6991,7 @@
       <c r="K3" t="b">
         <v>0</v>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -7022,6 +7033,7 @@
       <c r="K4" t="b">
         <v>0</v>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -7063,6 +7075,7 @@
       <c r="K5" t="b">
         <v>0</v>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -7104,6 +7117,11 @@
       <c r="K6" t="b">
         <v>1</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -7145,6 +7163,7 @@
       <c r="K7" t="b">
         <v>0</v>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -7186,6 +7205,7 @@
       <c r="K8" t="b">
         <v>0</v>
       </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -7227,6 +7247,7 @@
       <c r="K9" t="b">
         <v>0</v>
       </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -7268,6 +7289,11 @@
       <c r="K10" t="b">
         <v>1</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -7309,6 +7335,7 @@
       <c r="K11" t="b">
         <v>0</v>
       </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -7350,6 +7377,7 @@
       <c r="K12" t="b">
         <v>0</v>
       </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -7391,6 +7419,7 @@
       <c r="K13" t="b">
         <v>0</v>
       </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -7432,6 +7461,7 @@
       <c r="K14" t="b">
         <v>0</v>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -7473,6 +7503,7 @@
       <c r="K15" t="b">
         <v>0</v>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -7514,6 +7545,7 @@
       <c r="K16" t="b">
         <v>0</v>
       </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -7555,6 +7587,7 @@
       <c r="K17" t="b">
         <v>0</v>
       </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -7596,6 +7629,7 @@
       <c r="K18" t="b">
         <v>0</v>
       </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -7636,6 +7670,11 @@
       </c>
       <c r="K19" t="b">
         <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -7674,6 +7713,7 @@
       <c r="K20" t="b">
         <v>0</v>
       </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -7711,6 +7751,7 @@
       <c r="K21" t="b">
         <v>0</v>
       </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -7752,6 +7793,7 @@
       <c r="K22" t="b">
         <v>0</v>
       </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -7793,6 +7835,7 @@
       <c r="K23" t="b">
         <v>0</v>
       </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -7834,6 +7877,7 @@
       <c r="K24" t="b">
         <v>0</v>
       </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7875,6 +7919,7 @@
       <c r="K25" t="b">
         <v>0</v>
       </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -7916,6 +7961,11 @@
       <c r="K26" t="b">
         <v>1</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -7957,6 +8007,7 @@
       <c r="K27" t="b">
         <v>0</v>
       </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -7998,6 +8049,7 @@
       <c r="K28" t="b">
         <v>0</v>
       </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -8039,6 +8091,7 @@
       <c r="K29" t="b">
         <v>0</v>
       </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -8080,6 +8133,7 @@
       <c r="K30" t="b">
         <v>0</v>
       </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -8121,6 +8175,7 @@
       <c r="K31" t="b">
         <v>0</v>
       </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -8162,6 +8217,7 @@
       <c r="K32" t="b">
         <v>0</v>
       </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -8203,6 +8259,7 @@
       <c r="K33" t="b">
         <v>0</v>
       </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -8244,6 +8301,7 @@
       <c r="K34" t="b">
         <v>0</v>
       </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -8285,6 +8343,7 @@
       <c r="K35" t="b">
         <v>0</v>
       </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -8326,6 +8385,7 @@
       <c r="K36" t="b">
         <v>0</v>
       </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -8367,6 +8427,7 @@
       <c r="K37" t="b">
         <v>0</v>
       </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8408,6 +8469,7 @@
       <c r="K38" t="b">
         <v>0</v>
       </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8449,6 +8511,7 @@
       <c r="K39" t="b">
         <v>0</v>
       </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -8490,6 +8553,7 @@
       <c r="K40" t="b">
         <v>0</v>
       </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -8531,6 +8595,7 @@
       <c r="K41" t="b">
         <v>0</v>
       </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -8572,6 +8637,7 @@
       <c r="K42" t="b">
         <v>0</v>
       </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -8613,6 +8679,7 @@
       <c r="K43" t="b">
         <v>0</v>
       </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -8654,6 +8721,7 @@
       <c r="K44" t="b">
         <v>0</v>
       </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -8695,6 +8763,7 @@
       <c r="K45" t="b">
         <v>0</v>
       </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -8736,6 +8805,7 @@
       <c r="K46" t="b">
         <v>0</v>
       </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -8777,6 +8847,7 @@
       <c r="K47" t="b">
         <v>0</v>
       </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -8818,6 +8889,7 @@
       <c r="K48" t="b">
         <v>0</v>
       </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -8859,6 +8931,7 @@
       <c r="K49" t="b">
         <v>0</v>
       </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -8900,6 +8973,7 @@
       <c r="K50" t="b">
         <v>0</v>
       </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -8941,6 +9015,7 @@
       <c r="K51" t="b">
         <v>0</v>
       </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -8982,6 +9057,7 @@
       <c r="K52" t="b">
         <v>0</v>
       </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -9023,6 +9099,7 @@
       <c r="K53" t="b">
         <v>0</v>
       </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -9064,6 +9141,7 @@
       <c r="K54" t="b">
         <v>0</v>
       </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -9105,6 +9183,7 @@
       <c r="K55" t="b">
         <v>0</v>
       </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -9146,6 +9225,7 @@
       <c r="K56" t="b">
         <v>0</v>
       </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -9187,6 +9267,7 @@
       <c r="K57" t="b">
         <v>0</v>
       </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -9228,6 +9309,11 @@
       <c r="K58" t="b">
         <v>1</v>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -9269,6 +9355,7 @@
       <c r="K59" t="b">
         <v>0</v>
       </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -9310,6 +9397,7 @@
       <c r="K60" t="b">
         <v>0</v>
       </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -9351,6 +9439,7 @@
       <c r="K61" t="b">
         <v>0</v>
       </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -9392,6 +9481,7 @@
       <c r="K62" t="b">
         <v>0</v>
       </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -9433,6 +9523,7 @@
       <c r="K63" t="b">
         <v>0</v>
       </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -9474,6 +9565,7 @@
       <c r="K64" t="b">
         <v>0</v>
       </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -9515,6 +9607,7 @@
       <c r="K65" t="b">
         <v>0</v>
       </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -9556,6 +9649,11 @@
       <c r="K66" t="b">
         <v>1</v>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -9597,6 +9695,7 @@
       <c r="K67" t="b">
         <v>0</v>
       </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -9638,6 +9737,7 @@
       <c r="K68" t="b">
         <v>0</v>
       </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -9679,6 +9779,7 @@
       <c r="K69" t="b">
         <v>0</v>
       </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -9720,6 +9821,7 @@
       <c r="K70" t="b">
         <v>0</v>
       </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -9761,6 +9863,7 @@
       <c r="K71" t="b">
         <v>0</v>
       </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -9802,6 +9905,7 @@
       <c r="K72" t="b">
         <v>0</v>
       </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -9843,6 +9947,11 @@
       <c r="K73" t="b">
         <v>1</v>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -9884,6 +9993,7 @@
       <c r="K74" t="b">
         <v>0</v>
       </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -9925,6 +10035,7 @@
       <c r="K75" t="b">
         <v>0</v>
       </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -9966,6 +10077,7 @@
       <c r="K76" t="b">
         <v>0</v>
       </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -10007,6 +10119,7 @@
       <c r="K77" t="b">
         <v>0</v>
       </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -10048,6 +10161,7 @@
       <c r="K78" t="b">
         <v>0</v>
       </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -10089,6 +10203,7 @@
       <c r="K79" t="b">
         <v>0</v>
       </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -10130,6 +10245,7 @@
       <c r="K80" t="b">
         <v>0</v>
       </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -10171,6 +10287,7 @@
       <c r="K81" t="b">
         <v>0</v>
       </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -10212,6 +10329,7 @@
       <c r="K82" t="b">
         <v>0</v>
       </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -10253,6 +10371,7 @@
       <c r="K83" t="b">
         <v>0</v>
       </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -10294,6 +10413,7 @@
       <c r="K84" t="b">
         <v>0</v>
       </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -10335,6 +10455,7 @@
       <c r="K85" t="b">
         <v>0</v>
       </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -10376,6 +10497,7 @@
       <c r="K86" t="b">
         <v>0</v>
       </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -10417,6 +10539,7 @@
       <c r="K87" t="b">
         <v>0</v>
       </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -10458,6 +10581,7 @@
       <c r="K88" t="b">
         <v>0</v>
       </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -10499,6 +10623,7 @@
       <c r="K89" t="b">
         <v>0</v>
       </c>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -10540,6 +10665,7 @@
       <c r="K90" t="b">
         <v>0</v>
       </c>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -10581,6 +10707,7 @@
       <c r="K91" t="b">
         <v>0</v>
       </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -10622,6 +10749,7 @@
       <c r="K92" t="b">
         <v>0</v>
       </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -10663,6 +10791,7 @@
       <c r="K93" t="b">
         <v>0</v>
       </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -10704,6 +10833,7 @@
       <c r="K94" t="b">
         <v>0</v>
       </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -10745,6 +10875,7 @@
       <c r="K95" t="b">
         <v>0</v>
       </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -10786,6 +10917,7 @@
       <c r="K96" t="b">
         <v>0</v>
       </c>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -10827,6 +10959,7 @@
       <c r="K97" t="b">
         <v>0</v>
       </c>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -10868,6 +11001,11 @@
       <c r="K98" t="b">
         <v>1</v>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -10909,6 +11047,7 @@
       <c r="K99" t="b">
         <v>0</v>
       </c>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -10950,6 +11089,11 @@
       <c r="K100" t="b">
         <v>1</v>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -10991,6 +11135,7 @@
       <c r="K101" t="b">
         <v>0</v>
       </c>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -11032,6 +11177,7 @@
       <c r="K102" t="b">
         <v>0</v>
       </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -11073,6 +11219,7 @@
       <c r="K103" t="b">
         <v>0</v>
       </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -11114,6 +11261,7 @@
       <c r="K104" t="b">
         <v>0</v>
       </c>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -11155,6 +11303,7 @@
       <c r="K105" t="b">
         <v>0</v>
       </c>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -11196,6 +11345,7 @@
       <c r="K106" t="b">
         <v>0</v>
       </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -11237,6 +11387,7 @@
       <c r="K107" t="b">
         <v>0</v>
       </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -11278,6 +11429,7 @@
       <c r="K108" t="b">
         <v>0</v>
       </c>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -11319,6 +11471,7 @@
       <c r="K109" t="b">
         <v>0</v>
       </c>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -11360,6 +11513,7 @@
       <c r="K110" t="b">
         <v>0</v>
       </c>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -11401,6 +11555,7 @@
       <c r="K111" t="b">
         <v>0</v>
       </c>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -11442,6 +11597,7 @@
       <c r="K112" t="b">
         <v>0</v>
       </c>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -11483,6 +11639,7 @@
       <c r="K113" t="b">
         <v>0</v>
       </c>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -11524,6 +11681,7 @@
       <c r="K114" t="b">
         <v>0</v>
       </c>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -11565,6 +11723,7 @@
       <c r="K115" t="b">
         <v>0</v>
       </c>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -11606,6 +11765,7 @@
       <c r="K116" t="b">
         <v>0</v>
       </c>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -11647,6 +11807,7 @@
       <c r="K117" t="b">
         <v>0</v>
       </c>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -11688,6 +11849,7 @@
       <c r="K118" t="b">
         <v>0</v>
       </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -11729,6 +11891,7 @@
       <c r="K119" t="b">
         <v>0</v>
       </c>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -11770,6 +11933,7 @@
       <c r="K120" t="b">
         <v>0</v>
       </c>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -11811,6 +11975,7 @@
       <c r="K121" t="b">
         <v>0</v>
       </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -11852,6 +12017,7 @@
       <c r="K122" t="b">
         <v>0</v>
       </c>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -11893,6 +12059,7 @@
       <c r="K123" t="b">
         <v>0</v>
       </c>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -11934,6 +12101,7 @@
       <c r="K124" t="b">
         <v>0</v>
       </c>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -11975,6 +12143,7 @@
       <c r="K125" t="b">
         <v>0</v>
       </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -12016,6 +12185,7 @@
       <c r="K126" t="b">
         <v>0</v>
       </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -12057,6 +12227,7 @@
       <c r="K127" t="b">
         <v>0</v>
       </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -12098,6 +12269,7 @@
       <c r="K128" t="b">
         <v>0</v>
       </c>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -12139,6 +12311,7 @@
       <c r="K129" t="b">
         <v>0</v>
       </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -12180,6 +12353,7 @@
       <c r="K130" t="b">
         <v>0</v>
       </c>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -12221,6 +12395,7 @@
       <c r="K131" t="b">
         <v>0</v>
       </c>
+      <c r="L131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12233,7 +12408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12254,6 +12429,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>GT_panel</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>in_verkostung</t>
         </is>
       </c>
@@ -12274,7 +12454,12 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D2" t="b">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12294,7 +12479,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D3" t="b">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12314,7 +12500,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12334,7 +12521,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12354,7 +12542,12 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12374,7 +12567,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12394,7 +12588,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12414,7 +12609,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12434,7 +12630,12 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12454,7 +12655,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12474,7 +12676,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12494,7 +12697,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12514,7 +12718,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12534,7 +12739,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D15" t="b">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12554,7 +12760,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D16" t="b">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12574,7 +12781,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D17" t="b">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12594,7 +12802,8 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D18" t="b">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12614,7 +12823,12 @@
           <t>unpleasant</t>
         </is>
       </c>
-      <c r="D19" t="b">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>unpleasant</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12630,7 +12844,8 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="b">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12646,7 +12861,8 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="b">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12666,7 +12882,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D22" t="b">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12686,7 +12903,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D23" t="b">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12706,7 +12924,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D24" t="b">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12726,7 +12945,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D25" t="b">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12746,7 +12966,12 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D26" t="b">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Walderdbeere</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12766,7 +12991,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D27" t="b">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12786,7 +13012,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D28" t="b">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12806,7 +13033,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D29" t="b">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12826,7 +13054,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D30" t="b">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12846,7 +13075,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D31" t="b">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12866,7 +13096,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D32" t="b">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12886,7 +13117,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D33" t="b">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12906,7 +13138,8 @@
           <t>floral</t>
         </is>
       </c>
-      <c r="D34" t="b">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12926,7 +13159,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D35" t="b">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12946,7 +13180,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D36" t="b">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12966,7 +13201,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D37" t="b">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12986,7 +13222,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D38" t="b">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13006,7 +13243,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D39" t="b">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13026,7 +13264,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D40" t="b">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13046,7 +13285,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D41" t="b">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13066,7 +13306,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D42" t="b">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13086,7 +13327,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D43" t="b">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13106,7 +13348,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D44" t="b">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13126,7 +13369,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D45" t="b">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13146,7 +13390,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D46" t="b">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13166,7 +13411,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D47" t="b">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13186,7 +13432,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D48" t="b">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13206,7 +13453,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D49" t="b">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13226,7 +13474,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D50" t="b">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13246,7 +13495,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D51" t="b">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13266,7 +13516,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D52" t="b">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13286,7 +13537,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D53" t="b">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13306,7 +13558,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D54" t="b">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13326,7 +13579,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D55" t="b">
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13346,7 +13600,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D56" t="b">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13366,7 +13621,8 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D57" t="b">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13386,7 +13642,12 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D58" t="b">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13406,7 +13667,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D59" t="b">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13426,7 +13688,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D60" t="b">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13446,7 +13709,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D61" t="b">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13466,7 +13730,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D62" t="b">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13486,7 +13751,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D63" t="b">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13506,7 +13772,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D64" t="b">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13526,7 +13793,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D65" t="b">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13546,7 +13814,12 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D66" t="b">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="E66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13566,7 +13839,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D67" t="b">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13586,7 +13860,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D68" t="b">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13606,7 +13881,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D69" t="b">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13626,7 +13902,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D70" t="b">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13646,7 +13923,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D71" t="b">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13666,7 +13944,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D72" t="b">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13686,7 +13965,12 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D73" t="b">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E73" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13706,7 +13990,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D74" t="b">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13726,7 +14011,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D75" t="b">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13746,7 +14032,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D76" t="b">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13766,7 +14053,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D77" t="b">
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13786,7 +14074,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D78" t="b">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13806,7 +14095,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D79" t="b">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13826,7 +14116,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D80" t="b">
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13846,7 +14137,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D81" t="b">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13866,7 +14158,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D82" t="b">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13886,7 +14179,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D83" t="b">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13906,7 +14200,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D84" t="b">
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13926,7 +14221,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D85" t="b">
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13946,7 +14242,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D86" t="b">
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13966,7 +14263,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D87" t="b">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13986,7 +14284,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D88" t="b">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14006,7 +14305,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D89" t="b">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14026,7 +14326,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D90" t="b">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14046,7 +14347,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D91" t="b">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14066,7 +14368,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D92" t="b">
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14086,7 +14389,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D93" t="b">
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14106,7 +14410,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D94" t="b">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14126,7 +14431,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D95" t="b">
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14146,7 +14452,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D96" t="b">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14166,7 +14473,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D97" t="b">
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14186,7 +14494,12 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D98" t="b">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="E98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14206,7 +14519,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D99" t="b">
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14226,7 +14540,12 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D100" t="b">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14246,7 +14565,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D101" t="b">
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14266,7 +14586,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D102" t="b">
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14286,7 +14607,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D103" t="b">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14306,7 +14628,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D104" t="b">
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14326,7 +14649,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D105" t="b">
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14346,7 +14670,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D106" t="b">
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14366,7 +14691,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D107" t="b">
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14386,7 +14712,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D108" t="b">
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14406,7 +14733,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D109" t="b">
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14426,7 +14754,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D110" t="b">
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14446,7 +14775,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D111" t="b">
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14466,7 +14796,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D112" t="b">
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14486,7 +14817,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D113" t="b">
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14506,7 +14838,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D114" t="b">
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14526,7 +14859,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D115" t="b">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14546,7 +14880,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D116" t="b">
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14566,7 +14901,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D117" t="b">
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14586,7 +14922,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D118" t="b">
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14606,7 +14943,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D119" t="b">
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14626,7 +14964,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D120" t="b">
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14646,7 +14985,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D121" t="b">
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14666,7 +15006,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D122" t="b">
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14686,7 +15027,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D123" t="b">
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14706,7 +15048,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D124" t="b">
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14726,7 +15069,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D125" t="b">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14746,7 +15090,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D126" t="b">
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14766,7 +15111,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D127" t="b">
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14786,7 +15132,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D128" t="b">
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14806,7 +15153,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D129" t="b">
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14826,7 +15174,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D130" t="b">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14846,7 +15195,8 @@
           <t>warm</t>
         </is>
       </c>
-      <c r="D131" t="b">
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="b">
         <v>0</v>
       </c>
     </row>
